--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.94530094500125</v>
+        <v>9.903611403562703</v>
       </c>
       <c r="D2" t="n">
-        <v>7.501058095511587</v>
+        <v>1.218921940520633</v>
       </c>
       <c r="E2" t="n">
-        <v>19.47503507405412</v>
+        <v>3.164693199533794</v>
       </c>
       <c r="F2" t="n">
-        <v>9.972358594132457</v>
+        <v>1.620508271546524</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.55546980237712</v>
+        <v>10.81526384288628</v>
       </c>
       <c r="D3" t="n">
-        <v>30.96313486257313</v>
+        <v>5.031509415168134</v>
       </c>
       <c r="E3" t="n">
-        <v>19.47503507405412</v>
+        <v>3.164693199533794</v>
       </c>
       <c r="F3" t="n">
-        <v>9.972358594132457</v>
+        <v>1.620508271546524</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.72428436281846</v>
+        <v>3.692696208957999</v>
       </c>
       <c r="D4" t="n">
-        <v>13.34448855924703</v>
+        <v>2.168479390877643</v>
       </c>
       <c r="E4" t="n">
-        <v>19.47503507405412</v>
+        <v>3.164693199533794</v>
       </c>
       <c r="F4" t="n">
-        <v>9.972358594132457</v>
+        <v>1.620508271546524</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
